--- a/Result/profitability/2338.xlsx
+++ b/Result/profitability/2338.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.32</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.07</v>
+        <v>-0.9349999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>13.60375</v>
+        <v>12.96125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.16</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.9299999999999999</v>
+        <v>-0.5075000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>14.21625</v>
+        <v>13.7575</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.27</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.48875</v>
+        <v>-0.32375</v>
       </c>
       <c r="N4" t="n">
-        <v>14.78375</v>
+        <v>15.23125</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.37</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.385</v>
+        <v>-0.13875</v>
       </c>
       <c r="N5" t="n">
-        <v>14.89375</v>
+        <v>15.84</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.24</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.18375</v>
+        <v>-0.09125000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>14.50875</v>
+        <v>15.46625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.11</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.09250000000000001</v>
+        <v>0.11125</v>
       </c>
       <c r="N7" t="n">
-        <v>16.39375</v>
+        <v>17.565</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.18</v>
       </c>
       <c r="M8" t="n">
-        <v>0.11875</v>
+        <v>0.06874999999999998</v>
       </c>
       <c r="N8" t="n">
-        <v>18.7725</v>
+        <v>18.425</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2338</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1514</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1290</v>
+      </c>
+      <c r="E75" t="n">
+        <v>224</v>
+      </c>
+      <c r="F75" t="n">
+        <v>14.77</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-12</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-0.80%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>56</v>
+      </c>
+      <c r="J75" t="n">
+        <v>44</v>
+      </c>
+      <c r="K75" t="n">
+        <v>39</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-1.095</v>
+      </c>
+      <c r="N75" t="n">
+        <v>12.69625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.7692307692307693</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-2.780000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1584045584045585</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.064864864864865</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>7.569999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>1.051388888888889</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
